--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$104</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4070" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4032" uniqueCount="679">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:45:50+00:00</t>
+    <t>2023-04-26T08:27:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -326,6 +326,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -400,10 +404,6 @@
     <t>Meta.versionId</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
     <t>Observation.meta.lastUpdated</t>
   </si>
   <si>
@@ -460,14 +460,7 @@
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
-</t>
-  </si>
-  <si>
     <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Observation.meta.profile:MesFrObservationBodyHeight</t>
   </si>
   <si>
     <t>Observation.meta.security</t>
@@ -2448,12 +2441,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP105"/>
+  <dimension ref="A1:AP104"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.453125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="49.3046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.37109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.42578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2875,7 +2868,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>88</v>
@@ -2959,7 +2952,7 @@
         <v>100</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>78</v>
@@ -2971,7 +2964,7 @@
         <v>78</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>78</v>
@@ -2982,10 +2975,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -3008,13 +3001,13 @@
         <v>78</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -3065,7 +3058,7 @@
         <v>78</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -3089,7 +3082,7 @@
         <v>78</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>78</v>
@@ -3100,14 +3093,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -3126,16 +3119,16 @@
         <v>78</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3173,19 +3166,19 @@
         <v>78</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -3197,7 +3190,7 @@
         <v>100</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>78</v>
@@ -3209,7 +3202,7 @@
         <v>78</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>78</v>
@@ -3220,10 +3213,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -3249,13 +3242,13 @@
         <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3305,7 +3298,7 @@
         <v>78</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -3317,7 +3310,7 @@
         <v>100</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>78</v>
@@ -3329,7 +3322,7 @@
         <v>78</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>78</v>
@@ -3437,7 +3430,7 @@
         <v>100</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>78</v>
@@ -3449,7 +3442,7 @@
         <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>78</v>
@@ -3557,7 +3550,7 @@
         <v>100</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>78</v>
@@ -3569,7 +3562,7 @@
         <v>78</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>78</v>
@@ -3591,7 +3584,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>77</v>
@@ -3653,17 +3646,19 @@
         <v>78</v>
       </c>
       <c r="AB10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF10" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="AC10" s="2"/>
-      <c r="AD10" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -3675,7 +3670,7 @@
         <v>100</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>78</v>
@@ -3687,7 +3682,7 @@
         <v>78</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>78</v>
@@ -3698,26 +3693,24 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>7</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>78</v>
@@ -3726,16 +3719,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3746,7 +3739,7 @@
         <v>78</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>78</v>
@@ -3761,13 +3754,13 @@
         <v>78</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>78</v>
@@ -3785,7 +3778,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -3797,7 +3790,7 @@
         <v>100</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>78</v>
@@ -3806,10 +3799,10 @@
         <v>78</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>78</v>
@@ -3820,10 +3813,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3846,16 +3839,16 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3881,13 +3874,13 @@
         <v>78</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>78</v>
@@ -3905,7 +3898,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3917,7 +3910,7 @@
         <v>100</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>78</v>
@@ -3926,10 +3919,10 @@
         <v>78</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>78</v>
@@ -3940,10 +3933,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3954,28 +3947,28 @@
         <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4001,13 +3994,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -4025,19 +4018,19 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>78</v>
@@ -4046,10 +4039,10 @@
         <v>78</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>78</v>
@@ -4060,10 +4053,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4080,22 +4073,22 @@
         <v>78</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4121,13 +4114,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -4145,7 +4138,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -4157,7 +4150,7 @@
         <v>100</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
@@ -4169,7 +4162,7 @@
         <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>78</v>
@@ -4180,14 +4173,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4206,16 +4199,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4241,13 +4234,13 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -4265,7 +4258,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -4277,7 +4270,7 @@
         <v>100</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>78</v>
@@ -4289,7 +4282,7 @@
         <v>78</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>78</v>
@@ -4300,21 +4293,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>78</v>
@@ -4326,16 +4319,16 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4385,19 +4378,19 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
@@ -4409,7 +4402,7 @@
         <v>78</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>185</v>
+        <v>102</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>78</v>
@@ -4420,14 +4413,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4446,16 +4439,16 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>188</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>191</v>
+        <v>114</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4493,19 +4486,19 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -4514,10 +4507,10 @@
         <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
@@ -4529,7 +4522,7 @@
         <v>78</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>78</v>
@@ -4540,21 +4533,23 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>78</v>
@@ -4566,17 +4561,15 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4613,19 +4606,19 @@
         <v>78</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -4637,7 +4630,7 @@
         <v>100</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>78</v>
@@ -4649,7 +4642,7 @@
         <v>78</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>78</v>
@@ -4660,16 +4653,16 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4679,7 +4672,7 @@
         <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>78</v>
@@ -4688,15 +4681,17 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -4745,7 +4740,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -4757,7 +4752,7 @@
         <v>100</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
@@ -4769,7 +4764,7 @@
         <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>78</v>
@@ -4780,46 +4775,46 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I20" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I20" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>202</v>
+        <v>111</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
       </c>
@@ -4855,19 +4850,19 @@
         <v>78</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -4879,7 +4874,7 @@
         <v>100</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -4891,7 +4886,7 @@
         <v>78</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>78</v>
@@ -4902,14 +4897,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4922,25 +4917,23 @@
         <v>78</v>
       </c>
       <c r="I21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J21" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4977,19 +4970,19 @@
         <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -5001,22 +4994,22 @@
         <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>78</v>
@@ -5024,14 +5017,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5050,17 +5043,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -5109,7 +5104,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -5121,22 +5116,22 @@
         <v>100</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>78</v>
@@ -5144,14 +5139,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5170,20 +5165,18 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -5231,7 +5224,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -5243,19 +5236,19 @@
         <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>78</v>
@@ -5266,44 +5259,46 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>168</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
       </c>
@@ -5327,13 +5322,13 @@
         <v>78</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>78</v>
@@ -5351,34 +5346,34 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>78</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>78</v>
@@ -5386,10 +5381,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5400,31 +5395,31 @@
         <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>89</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>170</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -5449,58 +5444,56 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>244</v>
+        <v>172</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>78</v>
@@ -5508,12 +5501,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
       </c>
@@ -5522,7 +5517,7 @@
         <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>89</v>
@@ -5534,19 +5529,19 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5571,29 +5566,31 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -5605,7 +5602,7 @@
         <v>100</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
@@ -5614,13 +5611,13 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>78</v>
@@ -5631,23 +5628,21 @@
         <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C27" t="s" s="2">
         <v>265</v>
       </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>78</v>
@@ -5656,20 +5651,16 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -5693,13 +5684,13 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -5717,19 +5708,19 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>107</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -5738,13 +5729,13 @@
         <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>262</v>
+        <v>108</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>78</v>
@@ -5759,14 +5750,14 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -5778,15 +5769,17 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -5823,31 +5816,31 @@
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>78</v>
@@ -5859,7 +5852,7 @@
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>78</v>
@@ -5877,37 +5870,39 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
@@ -5943,19 +5938,19 @@
         <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5967,7 +5962,7 @@
         <v>100</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
@@ -5976,10 +5971,10 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>78</v>
@@ -5990,10 +5985,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6001,35 +5996,31 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G30" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G30" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
@@ -6077,19 +6068,19 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
@@ -6098,10 +6089,10 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>78</v>
@@ -6119,14 +6110,14 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
@@ -6138,15 +6129,17 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -6183,31 +6176,31 @@
         <v>78</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>78</v>
@@ -6219,7 +6212,7 @@
         <v>78</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -6237,43 +6230,45 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>78</v>
@@ -6303,31 +6298,31 @@
         <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
@@ -6336,10 +6331,10 @@
         <v>78</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -6350,10 +6345,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6361,13 +6356,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>78</v>
@@ -6376,26 +6371,24 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>78</v>
@@ -6437,7 +6430,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -6449,7 +6442,7 @@
         <v>100</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
@@ -6458,10 +6451,10 @@
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
@@ -6472,10 +6465,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6483,13 +6476,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>78</v>
@@ -6498,24 +6491,26 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>78</v>
@@ -6557,7 +6552,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -6569,7 +6564,7 @@
         <v>100</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
@@ -6578,10 +6573,10 @@
         <v>78</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>78</v>
@@ -6592,10 +6587,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6603,13 +6598,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>78</v>
@@ -6618,26 +6613,26 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O35" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>307</v>
+        <v>78</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>78</v>
@@ -6679,7 +6674,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -6691,7 +6686,7 @@
         <v>100</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>78</v>
@@ -6700,10 +6695,10 @@
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>78</v>
@@ -6714,10 +6709,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6740,19 +6735,19 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6801,7 +6796,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6813,7 +6808,7 @@
         <v>100</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>78</v>
@@ -6822,10 +6817,10 @@
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>78</v>
@@ -6836,10 +6831,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6862,19 +6857,19 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6923,7 +6918,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6935,7 +6930,7 @@
         <v>100</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>78</v>
@@ -6944,10 +6939,10 @@
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>78</v>
@@ -6958,24 +6953,24 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>78</v>
@@ -6984,19 +6979,19 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>251</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -7021,13 +7016,13 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -7045,10 +7040,10 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>88</v>
@@ -7057,69 +7052,65 @@
         <v>100</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>78</v>
+        <v>345</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>78</v>
+        <v>348</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>78</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>340</v>
+        <v>105</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
@@ -7143,13 +7134,13 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>345</v>
+        <v>78</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
@@ -7167,56 +7158,56 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>107</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>346</v>
+        <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>347</v>
+        <v>78</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>348</v>
+        <v>78</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>349</v>
+        <v>108</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>350</v>
+        <v>78</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>351</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
@@ -7228,15 +7219,17 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -7273,31 +7266,31 @@
         <v>78</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
@@ -7309,7 +7302,7 @@
         <v>78</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>78</v>
@@ -7320,14 +7313,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7343,21 +7336,23 @@
         <v>78</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
@@ -7393,19 +7388,17 @@
         <v>78</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -7417,7 +7410,7 @@
         <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>78</v>
@@ -7426,10 +7419,10 @@
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>78</v>
@@ -7443,18 +7436,20 @@
         <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -7466,19 +7461,19 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7515,17 +7510,19 @@
         <v>78</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -7537,7 +7534,7 @@
         <v>100</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
@@ -7546,10 +7543,10 @@
         <v>78</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
@@ -7563,17 +7560,15 @@
         <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C43" t="s" s="2">
         <v>357</v>
       </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>88</v>
@@ -7585,23 +7580,19 @@
         <v>78</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
@@ -7649,19 +7640,19 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
@@ -7670,10 +7661,10 @@
         <v>78</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>78</v>
@@ -7691,14 +7682,14 @@
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -7710,15 +7701,17 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7755,31 +7748,31 @@
         <v>78</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>78</v>
@@ -7791,7 +7784,7 @@
         <v>78</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -7809,14 +7802,14 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>78</v>
@@ -7825,27 +7818,29 @@
         <v>78</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>78</v>
+        <v>362</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>78</v>
@@ -7875,31 +7870,31 @@
         <v>78</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
@@ -7908,10 +7903,10 @@
         <v>78</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
@@ -7922,10 +7917,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7933,7 +7928,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>88</v>
@@ -7948,26 +7943,24 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>364</v>
+        <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>78</v>
@@ -8009,7 +8002,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -8021,7 +8014,7 @@
         <v>100</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>78</v>
@@ -8030,10 +8023,10 @@
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -8055,7 +8048,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>88</v>
@@ -8070,24 +8063,26 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>78</v>
+        <v>367</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>78</v>
@@ -8129,7 +8124,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -8141,7 +8136,7 @@
         <v>100</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>78</v>
@@ -8150,10 +8145,10 @@
         <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
@@ -8164,10 +8159,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8175,7 +8170,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>88</v>
@@ -8190,26 +8185,26 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O48" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>369</v>
+        <v>78</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>78</v>
@@ -8251,7 +8246,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -8263,7 +8258,7 @@
         <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>78</v>
@@ -8272,10 +8267,10 @@
         <v>78</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>78</v>
@@ -8312,19 +8307,19 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -8373,7 +8368,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -8385,7 +8380,7 @@
         <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
@@ -8394,10 +8389,10 @@
         <v>78</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
@@ -8411,7 +8406,7 @@
         <v>372</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8434,19 +8429,19 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -8495,7 +8490,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -8507,7 +8502,7 @@
         <v>100</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>78</v>
@@ -8516,10 +8511,10 @@
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -8530,10 +8525,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8541,13 +8536,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>78</v>
@@ -8556,19 +8551,19 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>103</v>
+        <v>374</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>331</v>
+        <v>375</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>332</v>
+        <v>376</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>333</v>
+        <v>377</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>334</v>
+        <v>378</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -8617,7 +8612,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -8629,22 +8624,22 @@
         <v>100</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>78</v>
+        <v>379</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>336</v>
+        <v>380</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>337</v>
+        <v>381</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>78</v>
+        <v>382</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>78</v>
@@ -8652,10 +8647,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8663,13 +8658,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>78</v>
@@ -8678,20 +8673,18 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
@@ -8739,34 +8732,34 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>78</v>
@@ -8774,21 +8767,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
@@ -8800,18 +8793,20 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8859,34 +8854,34 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>78</v>
+        <v>396</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>348</v>
+        <v>397</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>78</v>
@@ -8894,24 +8889,24 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>78</v>
@@ -8920,19 +8915,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8981,7 +8976,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -8990,25 +8985,25 @@
         <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>100</v>
+        <v>407</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>226</v>
+        <v>408</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>78</v>
@@ -9016,24 +9011,24 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>78</v>
@@ -9042,20 +9037,18 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>404</v>
+        <v>126</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -9103,7 +9096,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -9112,25 +9105,25 @@
         <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>409</v>
+        <v>100</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>410</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>411</v>
+        <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>78</v>
@@ -9138,10 +9131,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9152,7 +9145,7 @@
         <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
@@ -9164,18 +9157,20 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>126</v>
+        <v>421</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
       </c>
@@ -9223,34 +9218,34 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>78</v>
@@ -9258,10 +9253,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9272,10 +9267,10 @@
         <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>78</v>
@@ -9284,19 +9279,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>224</v>
+        <v>432</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -9333,59 +9328,59 @@
         <v>78</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>78</v>
+        <v>435</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>100</v>
+        <v>436</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>427</v>
+        <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>78</v>
+        <v>437</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>430</v>
+        <v>78</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>78</v>
+        <v>440</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C58" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="D58" t="s" s="2">
         <v>78</v>
       </c>
@@ -9406,19 +9401,19 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -9428,7 +9423,7 @@
         <v>78</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>78</v>
@@ -9455,17 +9450,19 @@
         <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AC58" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -9474,40 +9471,38 @@
         <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AJ58" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>442</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9519,29 +9514,25 @@
         <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>432</v>
+        <v>104</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>433</v>
+        <v>105</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9550,7 +9541,7 @@
         <v>78</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>445</v>
+        <v>78</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>78</v>
@@ -9589,7 +9580,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>431</v>
+        <v>107</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -9598,28 +9589,28 @@
         <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>438</v>
+        <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>439</v>
+        <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>440</v>
+        <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>441</v>
+        <v>108</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>442</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" hidden="true">
@@ -9631,14 +9622,14 @@
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9650,15 +9641,17 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9695,31 +9688,31 @@
         <v>78</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
@@ -9731,7 +9724,7 @@
         <v>78</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -9749,37 +9742,39 @@
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>110</v>
+        <v>450</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>111</v>
+        <v>451</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>112</v>
+        <v>452</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9815,31 +9810,31 @@
         <v>78</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>117</v>
+        <v>455</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
@@ -9848,10 +9843,10 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>101</v>
+        <v>457</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9862,10 +9857,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9873,39 +9868,41 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I62" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>452</v>
+        <v>168</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>455</v>
+        <v>303</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q62" s="2"/>
+      <c r="Q62" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="R62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9925,13 +9922,13 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>78</v>
+        <v>464</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>78</v>
+        <v>465</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -9949,7 +9946,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -9961,7 +9958,7 @@
         <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
@@ -9970,10 +9967,10 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>78</v>
@@ -9984,10 +9981,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9995,41 +9992,39 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q63" t="s" s="2">
-        <v>465</v>
-      </c>
+      <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
         <v>78</v>
       </c>
@@ -10049,13 +10044,13 @@
         <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>466</v>
+        <v>78</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>467</v>
+        <v>78</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -10073,7 +10068,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -10085,7 +10080,7 @@
         <v>100</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
@@ -10094,10 +10089,10 @@
         <v>78</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -10108,10 +10103,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10134,26 +10129,26 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>305</v>
+        <v>481</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>78</v>
+        <v>483</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>78</v>
@@ -10195,7 +10190,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -10204,10 +10199,10 @@
         <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>100</v>
+        <v>485</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
@@ -10216,10 +10211,10 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -10230,10 +10225,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10256,26 +10251,26 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>485</v>
+        <v>78</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>78</v>
@@ -10293,13 +10288,13 @@
         <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>78</v>
+        <v>492</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>78</v>
+        <v>493</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -10317,7 +10312,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -10326,10 +10321,10 @@
         <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>487</v>
+        <v>100</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
@@ -10338,10 +10333,10 @@
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -10352,10 +10347,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10363,7 +10358,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>88</v>
@@ -10375,22 +10370,22 @@
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>170</v>
+        <v>251</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -10415,13 +10410,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>244</v>
+        <v>148</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -10448,10 +10443,10 @@
         <v>88</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>100</v>
+        <v>503</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
@@ -10460,10 +10455,10 @@
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>477</v>
+        <v>102</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -10474,10 +10469,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10491,7 +10486,7 @@
         <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>78</v>
@@ -10500,20 +10495,16 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>499</v>
+        <v>105</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
       </c>
@@ -10537,13 +10528,13 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>503</v>
+        <v>78</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>504</v>
+        <v>78</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -10561,7 +10552,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>498</v>
+        <v>107</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -10570,10 +10561,10 @@
         <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
@@ -10582,10 +10573,10 @@
         <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>506</v>
+        <v>108</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -10596,21 +10587,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
@@ -10622,15 +10613,17 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10667,31 +10660,31 @@
         <v>78</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
@@ -10703,7 +10696,7 @@
         <v>78</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -10714,14 +10707,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10737,21 +10730,23 @@
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10787,19 +10782,19 @@
         <v>78</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -10811,7 +10806,7 @@
         <v>100</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
@@ -10820,10 +10815,10 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -10834,10 +10829,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10848,7 +10843,7 @@
         <v>76</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -10857,23 +10852,19 @@
         <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
       </c>
@@ -10921,19 +10912,19 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
@@ -10942,10 +10933,10 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -10956,21 +10947,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
@@ -10982,15 +10973,17 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -11027,31 +11020,31 @@
         <v>78</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>78</v>
@@ -11063,7 +11056,7 @@
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -11074,21 +11067,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
@@ -11097,21 +11090,23 @@
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -11147,31 +11142,31 @@
         <v>78</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
@@ -11180,10 +11175,10 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -11194,10 +11189,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11205,7 +11200,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>88</v>
@@ -11220,20 +11215,18 @@
         <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -11281,7 +11274,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -11293,7 +11286,7 @@
         <v>100</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
@@ -11302,10 +11295,10 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>78</v>
@@ -11316,10 +11309,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11327,7 +11320,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>88</v>
@@ -11342,18 +11335,20 @@
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
       </c>
@@ -11401,7 +11396,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -11413,7 +11408,7 @@
         <v>100</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
@@ -11422,10 +11417,10 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>78</v>
@@ -11436,10 +11431,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11447,7 +11442,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>88</v>
@@ -11462,19 +11457,19 @@
         <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -11523,7 +11518,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -11535,7 +11530,7 @@
         <v>100</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -11544,10 +11539,10 @@
         <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
@@ -11558,10 +11553,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11584,19 +11579,19 @@
         <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -11645,7 +11640,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -11657,7 +11652,7 @@
         <v>100</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
@@ -11666,10 +11661,10 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -11680,10 +11675,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11706,19 +11701,19 @@
         <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -11767,7 +11762,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -11779,7 +11774,7 @@
         <v>100</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
@@ -11788,10 +11783,10 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>78</v>
@@ -11802,21 +11797,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>78</v>
+        <v>517</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11825,22 +11820,22 @@
         <v>78</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>103</v>
+        <v>251</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>331</v>
+        <v>518</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>332</v>
+        <v>519</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>333</v>
+        <v>520</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>334</v>
+        <v>521</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11865,13 +11860,13 @@
         <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>78</v>
+        <v>523</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>78</v>
@@ -11889,49 +11884,49 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>335</v>
+        <v>516</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>78</v>
+        <v>524</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>336</v>
+        <v>525</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>337</v>
+        <v>526</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>78</v>
+        <v>527</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>519</v>
+        <v>78</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11950,19 +11945,19 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>253</v>
+        <v>529</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11987,13 +11982,13 @@
         <v>78</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>524</v>
+        <v>78</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>525</v>
+        <v>78</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>78</v>
@@ -12011,7 +12006,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -12023,33 +12018,33 @@
         <v>100</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>526</v>
+        <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>529</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12060,7 +12055,7 @@
         <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>78</v>
@@ -12072,20 +12067,18 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>531</v>
+        <v>251</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
       </c>
@@ -12109,13 +12102,13 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>78</v>
+        <v>540</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>78</v>
+        <v>541</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -12133,45 +12126,45 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>78</v>
+        <v>542</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>78</v>
+        <v>545</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12194,18 +12187,20 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
       </c>
@@ -12229,13 +12224,13 @@
         <v>78</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>160</v>
+        <v>242</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>78</v>
@@ -12253,7 +12248,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -12265,33 +12260,33 @@
         <v>100</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>544</v>
+        <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>547</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12314,20 +12309,18 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>253</v>
+        <v>556</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>78</v>
       </c>
@@ -12351,13 +12344,13 @@
         <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>553</v>
+        <v>78</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>554</v>
+        <v>78</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -12375,7 +12368,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -12387,33 +12380,33 @@
         <v>100</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>78</v>
+        <v>560</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>78</v>
+        <v>563</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12436,16 +12429,16 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12495,7 +12488,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -12507,33 +12500,33 @@
         <v>100</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>565</v>
+        <v>572</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12544,7 +12537,7 @@
         <v>76</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -12556,18 +12549,20 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
       </c>
@@ -12615,45 +12610,45 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>226</v>
+        <v>579</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>571</v>
+        <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>574</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12664,7 +12659,7 @@
         <v>76</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
@@ -12676,20 +12671,16 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>576</v>
+        <v>104</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>577</v>
+        <v>105</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12737,19 +12728,19 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>575</v>
+        <v>107</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>581</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
@@ -12758,10 +12749,10 @@
         <v>78</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>582</v>
+        <v>78</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>583</v>
+        <v>108</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>78</v>
@@ -12772,21 +12763,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>78</v>
@@ -12798,15 +12789,17 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -12843,31 +12836,31 @@
         <v>78</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
@@ -12879,7 +12872,7 @@
         <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>78</v>
@@ -12890,14 +12883,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>109</v>
+        <v>585</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12910,24 +12903,26 @@
         <v>78</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>111</v>
+        <v>586</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>112</v>
+        <v>587</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12963,19 +12958,19 @@
         <v>78</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>117</v>
+        <v>588</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -12987,7 +12982,7 @@
         <v>100</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>78</v>
@@ -12999,7 +12994,7 @@
         <v>78</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
@@ -13010,46 +13005,44 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>587</v>
+        <v>78</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>110</v>
+        <v>590</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>78</v>
       </c>
@@ -13097,19 +13090,19 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>100</v>
+        <v>594</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>118</v>
+        <v>595</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>78</v>
@@ -13118,10 +13111,10 @@
         <v>78</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>78</v>
+        <v>596</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>101</v>
+        <v>597</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>78</v>
@@ -13132,10 +13125,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13158,16 +13151,16 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13217,7 +13210,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -13226,22 +13219,22 @@
         <v>88</v>
       </c>
       <c r="AI89" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AJ89" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>598</v>
-      </c>
       <c r="AN89" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>78</v>
@@ -13252,10 +13245,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13278,18 +13271,20 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>592</v>
+        <v>251</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>605</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
@@ -13313,13 +13308,13 @@
         <v>78</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>78</v>
+        <v>607</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>78</v>
+        <v>608</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>78</v>
@@ -13337,7 +13332,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -13346,22 +13341,22 @@
         <v>88</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>596</v>
+        <v>100</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>597</v>
+        <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>78</v>
+        <v>609</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>603</v>
+        <v>526</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>78</v>
@@ -13372,10 +13367,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13386,7 +13381,7 @@
         <v>76</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>78</v>
@@ -13398,19 +13393,19 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -13435,13 +13430,13 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -13459,31 +13454,31 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>78</v>
@@ -13494,10 +13489,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13508,7 +13503,7 @@
         <v>76</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>78</v>
@@ -13520,19 +13515,19 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>253</v>
+        <v>619</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -13557,55 +13552,55 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>613</v>
-      </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>124</v>
+        <v>624</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>611</v>
+        <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>612</v>
+        <v>625</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>528</v>
+        <v>626</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>78</v>
@@ -13616,10 +13611,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13642,20 +13637,18 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>621</v>
+        <v>104</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>625</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>78</v>
       </c>
@@ -13703,7 +13696,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -13715,7 +13708,7 @@
         <v>100</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>626</v>
+        <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>78</v>
@@ -13724,10 +13717,10 @@
         <v>78</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>627</v>
+        <v>596</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>78</v>
@@ -13738,10 +13731,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13752,7 +13745,7 @@
         <v>76</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
@@ -13761,19 +13754,19 @@
         <v>78</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>103</v>
+        <v>632</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>305</v>
+        <v>635</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13823,19 +13816,19 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>78</v>
@@ -13844,10 +13837,10 @@
         <v>78</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>598</v>
+        <v>636</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>78</v>
@@ -13858,10 +13851,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13884,16 +13877,16 @@
         <v>89</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13943,7 +13936,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -13955,7 +13948,7 @@
         <v>100</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>78</v>
@@ -13964,10 +13957,10 @@
         <v>78</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>78</v>
@@ -13978,10 +13971,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13995,7 +13988,7 @@
         <v>77</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>78</v>
@@ -14004,18 +13997,20 @@
         <v>89</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>641</v>
+        <v>574</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>646</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>647</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
@@ -14063,7 +14058,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -14075,7 +14070,7 @@
         <v>100</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>226</v>
+        <v>648</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
@@ -14084,10 +14079,10 @@
         <v>78</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>78</v>
@@ -14098,10 +14093,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14112,32 +14107,28 @@
         <v>76</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>576</v>
+        <v>104</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>647</v>
+        <v>105</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>649</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>78</v>
       </c>
@@ -14185,19 +14176,19 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>646</v>
+        <v>107</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>650</v>
+        <v>78</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>78</v>
@@ -14206,10 +14197,10 @@
         <v>78</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>651</v>
+        <v>78</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>652</v>
+        <v>108</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>78</v>
@@ -14220,21 +14211,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
@@ -14246,15 +14237,17 @@
         <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>78</v>
@@ -14291,31 +14284,31 @@
         <v>78</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>78</v>
@@ -14327,7 +14320,7 @@
         <v>78</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>78</v>
@@ -14338,14 +14331,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>109</v>
+        <v>585</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14358,24 +14351,26 @@
         <v>78</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>111</v>
+        <v>586</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>112</v>
+        <v>587</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
       </c>
@@ -14411,19 +14406,19 @@
         <v>78</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>117</v>
+        <v>588</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -14435,7 +14430,7 @@
         <v>100</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>78</v>
@@ -14447,7 +14442,7 @@
         <v>78</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>78</v>
@@ -14458,45 +14453,45 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>587</v>
+        <v>78</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>110</v>
+        <v>251</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>588</v>
+        <v>655</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>589</v>
+        <v>656</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>113</v>
+        <v>657</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>208</v>
+        <v>658</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -14521,13 +14516,13 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -14545,34 +14540,34 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>590</v>
+        <v>654</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>78</v>
+        <v>659</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>78</v>
+        <v>346</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>101</v>
+        <v>347</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>78</v>
+        <v>348</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>78</v>
@@ -14580,10 +14575,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14591,7 +14586,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>88</v>
@@ -14606,19 +14601,19 @@
         <v>89</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>253</v>
+        <v>661</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>660</v>
+        <v>433</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -14643,13 +14638,13 @@
         <v>78</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>150</v>
+        <v>242</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>344</v>
+        <v>665</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>345</v>
+        <v>666</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -14667,45 +14662,45 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>100</v>
+        <v>667</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>348</v>
+        <v>438</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>349</v>
+        <v>439</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>350</v>
+        <v>78</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>78</v>
+        <v>440</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14725,22 +14720,22 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>663</v>
+        <v>251</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>435</v>
+        <v>500</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -14765,13 +14760,13 @@
         <v>78</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>244</v>
+        <v>148</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>667</v>
+        <v>501</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>668</v>
+        <v>502</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>78</v>
@@ -14789,7 +14784,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -14798,50 +14793,50 @@
         <v>88</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>670</v>
+        <v>78</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>440</v>
+        <v>102</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>441</v>
+        <v>504</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>442</v>
+        <v>78</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>78</v>
+        <v>517</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>78</v>
@@ -14850,19 +14845,19 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>672</v>
+        <v>518</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>673</v>
+        <v>519</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>674</v>
+        <v>520</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14887,13 +14882,13 @@
         <v>78</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>504</v>
+        <v>675</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>78</v>
@@ -14911,37 +14906,37 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>675</v>
+        <v>100</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>78</v>
+        <v>524</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>101</v>
+        <v>525</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>78</v>
+        <v>527</v>
       </c>
     </row>
     <row r="104" hidden="true">
@@ -14953,7 +14948,7 @@
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>519</v>
+        <v>78</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14972,19 +14967,19 @@
         <v>78</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>520</v>
+        <v>677</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>521</v>
+        <v>678</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>522</v>
+        <v>577</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>523</v>
+        <v>578</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -15009,13 +15004,13 @@
         <v>78</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>524</v>
+        <v>78</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>677</v>
+        <v>78</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>78</v>
@@ -15042,154 +15037,32 @@
         <v>77</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>526</v>
+        <v>78</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>527</v>
+        <v>580</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>528</v>
+        <v>581</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="P105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP105" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP105">
+  <autoFilter ref="A1:AP104">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15199,7 +15072,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI104">
+  <conditionalFormatting sqref="A2:AI103">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T08:27:54+00:00</t>
+    <t>2023-04-26T14:43:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T14:43:04+00:00</t>
+    <t>2023-04-27T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-27T16:49:23+00:00</t>
+    <t>2023-05-02T12:59:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T12:59:07+00:00</t>
+    <t>2023-05-02T13:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T13:06:55+00:00</t>
+    <t>2023-05-02T14:05:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:33:57+00:00</t>
+    <t>2023-07-18T09:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:34:12+00:00</t>
+    <t>2023-07-18T09:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:34:49+00:00</t>
+    <t>2023-07-18T09:37:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3990" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3989" uniqueCount="637">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:37:51+00:00</t>
+    <t>2023-09-19T16:09:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -143,6 +143,10 @@
     <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
   </si>
   <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}vs-2:If there is no component or hasMember element then either a value[x] or a data absent reason must be present. {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() or value.exists())}</t>
+  </si>
+  <si>
     <t>Event</t>
   </si>
   <si>
@@ -535,7 +539,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -622,7 +626,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -1091,7 +1095,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1149,7 +1153,7 @@
     <t>Often just a dateTime for Vital Signs.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -1184,7 +1188,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -1234,7 +1238,7 @@
     <t>Vital Signs value are recorded using the Quantity data type. For supporting observations such as Cuff size could use other datatypes such as CodeableConcept.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>9. SHALL contain exactly one [1..1] value with @xsi:type="PQ" (CONF:7305).</t>
@@ -1514,10 +1518,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>Codes identifying interpretations of observations.</t>
-  </si>
-  <si>
-    <t>http://www.interopsante.org/fhir/structuredefinition/observation/fr-obervation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1567,7 +1568,7 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](extension-bodysite.html).</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -1874,7 +1875,7 @@
     <t>Used when reporting vital signs panel components.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1896,7 +1897,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1908,7 +1909,7 @@
     <t>Used when reporting systolic and diastolic blood pressure.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
@@ -1965,7 +1966,7 @@
     <t>Vital Sign Value recorded with UCUM.</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Common UCUM units for recording Vital Signs.</t>
@@ -2001,7 +2002,7 @@
     <t>Observation.component.interpretation</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -2459,19 +2460,19 @@
         <v>36</v>
       </c>
       <c r="AJ1" t="s" s="2">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="AK1" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AL1" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AM1" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AN1" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AO1" t="s" s="2">
         <v>36</v>
@@ -2482,10 +2483,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2496,7 +2497,7 @@
         <v>34</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>36</v>
@@ -2505,19 +2506,19 @@
         <v>36</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2567,13 +2568,13 @@
         <v>36</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>36</v>
@@ -2602,10 +2603,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2616,7 +2617,7 @@
         <v>34</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>36</v>
@@ -2625,16 +2626,16 @@
         <v>36</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -2685,19 +2686,19 @@
         <v>36</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK3" t="s" s="2">
         <v>36</v>
@@ -2709,7 +2710,7 @@
         <v>36</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO3" t="s" s="2">
         <v>36</v>
@@ -2720,10 +2721,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2734,7 +2735,7 @@
         <v>34</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>36</v>
@@ -2746,13 +2747,13 @@
         <v>36</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2803,13 +2804,13 @@
         <v>36</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>36</v>
@@ -2827,7 +2828,7 @@
         <v>36</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>36</v>
@@ -2838,14 +2839,14 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
@@ -2864,16 +2865,16 @@
         <v>36</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2911,19 +2912,19 @@
         <v>36</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>34</v>
@@ -2932,10 +2933,10 @@
         <v>35</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>36</v>
@@ -2947,7 +2948,7 @@
         <v>36</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>36</v>
@@ -2958,10 +2959,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2972,7 +2973,7 @@
         <v>34</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>36</v>
@@ -2981,19 +2982,19 @@
         <v>36</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3043,19 +3044,19 @@
         <v>36</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>36</v>
@@ -3067,7 +3068,7 @@
         <v>36</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>36</v>
@@ -3078,10 +3079,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -3092,7 +3093,7 @@
         <v>34</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>36</v>
@@ -3101,19 +3102,19 @@
         <v>36</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3163,19 +3164,19 @@
         <v>36</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>36</v>
@@ -3187,7 +3188,7 @@
         <v>36</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>36</v>
@@ -3198,10 +3199,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -3212,7 +3213,7 @@
         <v>34</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>36</v>
@@ -3221,19 +3222,19 @@
         <v>36</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3283,19 +3284,19 @@
         <v>36</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>36</v>
@@ -3307,7 +3308,7 @@
         <v>36</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>36</v>
@@ -3318,10 +3319,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3341,19 +3342,19 @@
         <v>36</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3403,7 +3404,7 @@
         <v>36</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>34</v>
@@ -3412,10 +3413,10 @@
         <v>35</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>36</v>
@@ -3427,7 +3428,7 @@
         <v>36</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>36</v>
@@ -3438,10 +3439,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3461,19 +3462,19 @@
         <v>36</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3499,13 +3500,13 @@
         <v>36</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>36</v>
@@ -3523,7 +3524,7 @@
         <v>36</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>34</v>
@@ -3532,10 +3533,10 @@
         <v>35</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>36</v>
@@ -3544,10 +3545,10 @@
         <v>36</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>36</v>
@@ -3558,10 +3559,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3581,19 +3582,19 @@
         <v>36</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3619,13 +3620,13 @@
         <v>36</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>36</v>
@@ -3643,7 +3644,7 @@
         <v>36</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>34</v>
@@ -3652,10 +3653,10 @@
         <v>35</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>36</v>
@@ -3664,10 +3665,10 @@
         <v>36</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>36</v>
@@ -3678,10 +3679,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3692,28 +3693,28 @@
         <v>34</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>36</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3763,19 +3764,19 @@
         <v>36</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>36</v>
@@ -3787,7 +3788,7 @@
         <v>36</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>36</v>
@@ -3798,10 +3799,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3812,7 +3813,7 @@
         <v>34</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>36</v>
@@ -3824,16 +3825,16 @@
         <v>36</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3859,13 +3860,13 @@
         <v>36</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>36</v>
@@ -3883,19 +3884,19 @@
         <v>36</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>36</v>
@@ -3907,7 +3908,7 @@
         <v>36</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>36</v>
@@ -3918,21 +3919,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>36</v>
@@ -3944,16 +3945,16 @@
         <v>36</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4003,19 +4004,19 @@
         <v>36</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>36</v>
@@ -4027,7 +4028,7 @@
         <v>36</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>36</v>
@@ -4038,14 +4039,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4064,16 +4065,16 @@
         <v>36</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4123,7 +4124,7 @@
         <v>36</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>34</v>
@@ -4147,7 +4148,7 @@
         <v>36</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>36</v>
@@ -4158,14 +4159,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4184,16 +4185,16 @@
         <v>36</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4231,19 +4232,19 @@
         <v>36</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>34</v>
@@ -4252,10 +4253,10 @@
         <v>35</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>36</v>
@@ -4267,7 +4268,7 @@
         <v>36</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>36</v>
@@ -4278,13 +4279,13 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>36</v>
@@ -4294,7 +4295,7 @@
         <v>34</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>36</v>
@@ -4306,13 +4307,13 @@
         <v>36</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4363,7 +4364,7 @@
         <v>36</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>34</v>
@@ -4372,10 +4373,10 @@
         <v>35</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>36</v>
@@ -4387,7 +4388,7 @@
         <v>36</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>36</v>
@@ -4398,26 +4399,26 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>36</v>
@@ -4426,16 +4427,16 @@
         <v>36</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4485,7 +4486,7 @@
         <v>36</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>34</v>
@@ -4494,10 +4495,10 @@
         <v>35</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>36</v>
@@ -4509,7 +4510,7 @@
         <v>36</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>36</v>
@@ -4520,14 +4521,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4540,25 +4541,25 @@
         <v>36</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>36</v>
@@ -4595,19 +4596,19 @@
         <v>36</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>34</v>
@@ -4616,10 +4617,10 @@
         <v>35</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>36</v>
@@ -4631,7 +4632,7 @@
         <v>36</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>36</v>
@@ -4642,10 +4643,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4665,20 +4666,20 @@
         <v>36</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>36</v>
@@ -4727,7 +4728,7 @@
         <v>36</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>34</v>
@@ -4736,25 +4737,25 @@
         <v>35</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>36</v>
@@ -4762,14 +4763,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4785,22 +4786,22 @@
         <v>36</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>36</v>
@@ -4849,7 +4850,7 @@
         <v>36</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>34</v>
@@ -4858,22 +4859,22 @@
         <v>35</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>36</v>
@@ -4884,14 +4885,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4907,19 +4908,19 @@
         <v>36</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4969,7 +4970,7 @@
         <v>36</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>34</v>
@@ -4978,22 +4979,22 @@
         <v>35</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>36</v>
@@ -5004,10 +5005,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5015,34 +5016,34 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>36</v>
@@ -5067,13 +5068,13 @@
         <v>36</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>36</v>
@@ -5091,34 +5092,34 @@
         <v>36</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>36</v>
@@ -5126,10 +5127,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5137,13 +5138,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>35</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>36</v>
@@ -5152,19 +5153,19 @@
         <v>36</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>36</v>
@@ -5189,29 +5190,29 @@
         <v>36</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>34</v>
@@ -5220,10 +5221,10 @@
         <v>35</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>36</v>
@@ -5232,13 +5233,13 @@
         <v>36</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>36</v>
@@ -5246,26 +5247,26 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>36</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>36</v>
@@ -5274,19 +5275,19 @@
         <v>36</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>36</v>
@@ -5311,13 +5312,13 @@
         <v>36</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>36</v>
@@ -5335,7 +5336,7 @@
         <v>36</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>34</v>
@@ -5344,10 +5345,10 @@
         <v>35</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>36</v>
@@ -5356,13 +5357,13 @@
         <v>36</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>36</v>
@@ -5370,10 +5371,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5384,7 +5385,7 @@
         <v>34</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>36</v>
@@ -5396,13 +5397,13 @@
         <v>36</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5453,13 +5454,13 @@
         <v>36</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>36</v>
@@ -5477,7 +5478,7 @@
         <v>36</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>36</v>
@@ -5488,14 +5489,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5514,16 +5515,16 @@
         <v>36</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5561,19 +5562,19 @@
         <v>36</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>34</v>
@@ -5582,10 +5583,10 @@
         <v>35</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>36</v>
@@ -5597,7 +5598,7 @@
         <v>36</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>36</v>
@@ -5608,10 +5609,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5619,34 +5620,34 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>35</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>36</v>
@@ -5695,7 +5696,7 @@
         <v>36</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>34</v>
@@ -5704,10 +5705,10 @@
         <v>35</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>36</v>
@@ -5716,10 +5717,10 @@
         <v>36</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>36</v>
@@ -5730,10 +5731,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5744,7 +5745,7 @@
         <v>34</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>36</v>
@@ -5756,13 +5757,13 @@
         <v>36</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5813,13 +5814,13 @@
         <v>36</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>36</v>
@@ -5837,7 +5838,7 @@
         <v>36</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>36</v>
@@ -5848,14 +5849,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5874,16 +5875,16 @@
         <v>36</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5921,19 +5922,19 @@
         <v>36</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>34</v>
@@ -5942,10 +5943,10 @@
         <v>35</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>36</v>
@@ -5957,7 +5958,7 @@
         <v>36</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>36</v>
@@ -5968,10 +5969,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5979,41 +5980,41 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>36</v>
@@ -6055,19 +6056,19 @@
         <v>36</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>36</v>
@@ -6076,10 +6077,10 @@
         <v>36</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>36</v>
@@ -6090,10 +6091,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6104,7 +6105,7 @@
         <v>34</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>36</v>
@@ -6113,19 +6114,19 @@
         <v>36</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6175,19 +6176,19 @@
         <v>36</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>36</v>
@@ -6196,10 +6197,10 @@
         <v>36</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>36</v>
@@ -6210,10 +6211,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6221,41 +6222,41 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>36</v>
@@ -6297,19 +6298,19 @@
         <v>36</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>36</v>
@@ -6318,10 +6319,10 @@
         <v>36</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>36</v>
@@ -6332,10 +6333,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6346,7 +6347,7 @@
         <v>34</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>36</v>
@@ -6355,22 +6356,22 @@
         <v>36</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>36</v>
@@ -6419,19 +6420,19 @@
         <v>36</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>36</v>
@@ -6440,10 +6441,10 @@
         <v>36</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>36</v>
@@ -6454,10 +6455,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6468,7 +6469,7 @@
         <v>34</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>36</v>
@@ -6477,22 +6478,22 @@
         <v>36</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>36</v>
@@ -6541,19 +6542,19 @@
         <v>36</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>36</v>
@@ -6562,10 +6563,10 @@
         <v>36</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>36</v>
@@ -6576,10 +6577,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6590,7 +6591,7 @@
         <v>34</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>36</v>
@@ -6599,22 +6600,22 @@
         <v>36</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>36</v>
@@ -6663,19 +6664,19 @@
         <v>36</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>36</v>
@@ -6684,10 +6685,10 @@
         <v>36</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>36</v>
@@ -6698,45 +6699,45 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>36</v>
@@ -6761,13 +6762,13 @@
         <v>36</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>36</v>
@@ -6785,45 +6786,45 @@
         <v>36</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6834,7 +6835,7 @@
         <v>34</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>36</v>
@@ -6846,13 +6847,13 @@
         <v>36</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6903,13 +6904,13 @@
         <v>36</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>36</v>
@@ -6927,7 +6928,7 @@
         <v>36</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>36</v>
@@ -6938,14 +6939,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6964,16 +6965,16 @@
         <v>36</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7011,19 +7012,19 @@
         <v>36</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>34</v>
@@ -7032,10 +7033,10 @@
         <v>35</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>36</v>
@@ -7047,7 +7048,7 @@
         <v>36</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>36</v>
@@ -7058,10 +7059,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7081,22 +7082,22 @@
         <v>36</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>36</v>
@@ -7133,17 +7134,17 @@
         <v>36</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>34</v>
@@ -7152,10 +7153,10 @@
         <v>35</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>36</v>
@@ -7164,10 +7165,10 @@
         <v>36</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>36</v>
@@ -7178,23 +7179,23 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>36</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>36</v>
@@ -7203,22 +7204,22 @@
         <v>36</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>36</v>
@@ -7267,7 +7268,7 @@
         <v>36</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>34</v>
@@ -7276,10 +7277,10 @@
         <v>35</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>36</v>
@@ -7288,10 +7289,10 @@
         <v>36</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>36</v>
@@ -7302,10 +7303,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7316,7 +7317,7 @@
         <v>34</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>36</v>
@@ -7328,13 +7329,13 @@
         <v>36</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7385,13 +7386,13 @@
         <v>36</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>36</v>
@@ -7409,7 +7410,7 @@
         <v>36</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>36</v>
@@ -7420,14 +7421,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7446,16 +7447,16 @@
         <v>36</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7493,19 +7494,19 @@
         <v>36</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>34</v>
@@ -7514,10 +7515,10 @@
         <v>35</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>36</v>
@@ -7529,7 +7530,7 @@
         <v>36</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>36</v>
@@ -7540,10 +7541,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7551,10 +7552,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>36</v>
@@ -7563,29 +7564,29 @@
         <v>36</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>36</v>
@@ -7627,19 +7628,19 @@
         <v>36</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>36</v>
@@ -7648,10 +7649,10 @@
         <v>36</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>36</v>
@@ -7662,10 +7663,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7676,7 +7677,7 @@
         <v>34</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>36</v>
@@ -7685,19 +7686,19 @@
         <v>36</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7747,19 +7748,19 @@
         <v>36</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>36</v>
@@ -7768,10 +7769,10 @@
         <v>36</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>36</v>
@@ -7782,10 +7783,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7793,10 +7794,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>36</v>
@@ -7805,29 +7806,29 @@
         <v>36</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>36</v>
@@ -7869,19 +7870,19 @@
         <v>36</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>36</v>
@@ -7890,10 +7891,10 @@
         <v>36</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>36</v>
@@ -7904,10 +7905,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7918,7 +7919,7 @@
         <v>34</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>36</v>
@@ -7927,22 +7928,22 @@
         <v>36</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>36</v>
@@ -7991,19 +7992,19 @@
         <v>36</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>36</v>
@@ -8012,10 +8013,10 @@
         <v>36</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>36</v>
@@ -8026,10 +8027,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8040,7 +8041,7 @@
         <v>34</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>36</v>
@@ -8049,22 +8050,22 @@
         <v>36</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>36</v>
@@ -8113,19 +8114,19 @@
         <v>36</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>36</v>
@@ -8134,10 +8135,10 @@
         <v>36</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>36</v>
@@ -8148,10 +8149,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8162,7 +8163,7 @@
         <v>34</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>36</v>
@@ -8171,22 +8172,22 @@
         <v>36</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>36</v>
@@ -8235,19 +8236,19 @@
         <v>36</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>36</v>
@@ -8256,10 +8257,10 @@
         <v>36</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>36</v>
@@ -8270,10 +8271,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8281,34 +8282,34 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>36</v>
@@ -8357,34 +8358,34 @@
         <v>36</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>36</v>
@@ -8392,10 +8393,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8415,19 +8416,19 @@
         <v>36</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8477,7 +8478,7 @@
         <v>36</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>34</v>
@@ -8486,10 +8487,10 @@
         <v>35</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>36</v>
@@ -8498,13 +8499,13 @@
         <v>36</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>36</v>
@@ -8512,21 +8513,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>36</v>
@@ -8535,22 +8536,22 @@
         <v>36</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>36</v>
@@ -8599,34 +8600,34 @@
         <v>36</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>36</v>
@@ -8634,45 +8635,45 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>36</v>
@@ -8721,34 +8722,34 @@
         <v>36</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>36</v>
@@ -8756,10 +8757,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8770,7 +8771,7 @@
         <v>34</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>36</v>
@@ -8779,19 +8780,19 @@
         <v>36</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8841,19 +8842,19 @@
         <v>36</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>36</v>
@@ -8862,13 +8863,13 @@
         <v>36</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>36</v>
@@ -8876,10 +8877,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8899,22 +8900,22 @@
         <v>36</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>36</v>
@@ -8963,7 +8964,7 @@
         <v>36</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>34</v>
@@ -8972,25 +8973,25 @@
         <v>35</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>36</v>
@@ -8998,10 +8999,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9012,31 +9013,31 @@
         <v>34</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>36</v>
@@ -9073,58 +9074,58 @@
         <v>36</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AC56" s="2"/>
       <c r="AD56" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>36</v>
@@ -9134,31 +9135,31 @@
         <v>34</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>36</v>
@@ -9168,7 +9169,7 @@
         <v>36</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>36</v>
@@ -9207,45 +9208,45 @@
         <v>36</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9256,7 +9257,7 @@
         <v>34</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>36</v>
@@ -9268,13 +9269,13 @@
         <v>36</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9325,13 +9326,13 @@
         <v>36</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>36</v>
@@ -9349,7 +9350,7 @@
         <v>36</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>36</v>
@@ -9360,14 +9361,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9386,16 +9387,16 @@
         <v>36</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9433,19 +9434,19 @@
         <v>36</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>34</v>
@@ -9454,10 +9455,10 @@
         <v>35</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>36</v>
@@ -9469,7 +9470,7 @@
         <v>36</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>36</v>
@@ -9480,10 +9481,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9491,34 +9492,34 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>36</v>
@@ -9567,19 +9568,19 @@
         <v>36</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>36</v>
@@ -9588,10 +9589,10 @@
         <v>36</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>36</v>
@@ -9602,10 +9603,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9616,37 +9617,37 @@
         <v>34</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>36</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q61" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="R61" t="s" s="2">
         <v>36</v>
@@ -9667,13 +9668,13 @@
         <v>36</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>36</v>
@@ -9691,19 +9692,19 @@
         <v>36</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>36</v>
@@ -9712,10 +9713,10 @@
         <v>36</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>36</v>
@@ -9726,10 +9727,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9737,34 +9738,34 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>36</v>
@@ -9813,19 +9814,19 @@
         <v>36</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>36</v>
@@ -9834,10 +9835,10 @@
         <v>36</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>36</v>
@@ -9848,10 +9849,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9859,41 +9860,41 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="S63" t="s" s="2">
         <v>36</v>
@@ -9935,19 +9936,19 @@
         <v>36</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>36</v>
@@ -9956,10 +9957,10 @@
         <v>36</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>36</v>
@@ -9970,10 +9971,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9981,34 +9982,34 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>36</v>
@@ -10033,13 +10034,13 @@
         <v>36</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>36</v>
@@ -10057,19 +10058,19 @@
         <v>36</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>36</v>
@@ -10078,10 +10079,10 @@
         <v>36</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>36</v>
@@ -10092,10 +10093,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10106,10 +10107,10 @@
         <v>34</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>36</v>
@@ -10118,19 +10119,19 @@
         <v>36</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>36</v>
@@ -10155,13 +10156,13 @@
         <v>36</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>36</v>
@@ -10179,19 +10180,19 @@
         <v>36</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>36</v>
@@ -10200,10 +10201,10 @@
         <v>36</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>36</v>
@@ -10214,10 +10215,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10228,7 +10229,7 @@
         <v>34</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>36</v>
@@ -10240,13 +10241,13 @@
         <v>36</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10297,13 +10298,13 @@
         <v>36</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>36</v>
@@ -10321,7 +10322,7 @@
         <v>36</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>36</v>
@@ -10332,14 +10333,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10358,16 +10359,16 @@
         <v>36</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10405,19 +10406,19 @@
         <v>36</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>34</v>
@@ -10426,10 +10427,10 @@
         <v>35</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>36</v>
@@ -10441,7 +10442,7 @@
         <v>36</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>36</v>
@@ -10452,10 +10453,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10475,22 +10476,22 @@
         <v>36</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>36</v>
@@ -10539,7 +10540,7 @@
         <v>36</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>34</v>
@@ -10548,10 +10549,10 @@
         <v>35</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>36</v>
@@ -10560,10 +10561,10 @@
         <v>36</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>36</v>
@@ -10574,10 +10575,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10588,7 +10589,7 @@
         <v>34</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>36</v>
@@ -10600,13 +10601,13 @@
         <v>36</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10657,13 +10658,13 @@
         <v>36</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>36</v>
@@ -10681,7 +10682,7 @@
         <v>36</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>36</v>
@@ -10692,14 +10693,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10718,16 +10719,16 @@
         <v>36</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10765,19 +10766,19 @@
         <v>36</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>34</v>
@@ -10786,10 +10787,10 @@
         <v>35</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>36</v>
@@ -10801,7 +10802,7 @@
         <v>36</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>36</v>
@@ -10812,10 +10813,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10823,10 +10824,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>36</v>
@@ -10835,22 +10836,22 @@
         <v>36</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>36</v>
@@ -10899,19 +10900,19 @@
         <v>36</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>36</v>
@@ -10920,10 +10921,10 @@
         <v>36</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>36</v>
@@ -10934,10 +10935,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10948,7 +10949,7 @@
         <v>34</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>36</v>
@@ -10957,19 +10958,19 @@
         <v>36</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11019,19 +11020,19 @@
         <v>36</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>36</v>
@@ -11040,10 +11041,10 @@
         <v>36</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>36</v>
@@ -11054,10 +11055,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11065,10 +11066,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>36</v>
@@ -11077,22 +11078,22 @@
         <v>36</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>36</v>
@@ -11141,19 +11142,19 @@
         <v>36</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>36</v>
@@ -11162,10 +11163,10 @@
         <v>36</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>36</v>
@@ -11176,10 +11177,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11190,7 +11191,7 @@
         <v>34</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>36</v>
@@ -11199,22 +11200,22 @@
         <v>36</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>36</v>
@@ -11263,19 +11264,19 @@
         <v>36</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>36</v>
@@ -11284,10 +11285,10 @@
         <v>36</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>36</v>
@@ -11298,10 +11299,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11312,7 +11313,7 @@
         <v>34</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>36</v>
@@ -11321,22 +11322,22 @@
         <v>36</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>36</v>
@@ -11385,19 +11386,19 @@
         <v>36</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>36</v>
@@ -11406,10 +11407,10 @@
         <v>36</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>36</v>
@@ -11420,10 +11421,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11434,7 +11435,7 @@
         <v>34</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>36</v>
@@ -11443,22 +11444,22 @@
         <v>36</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>36</v>
@@ -11507,19 +11508,19 @@
         <v>36</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>36</v>
@@ -11528,10 +11529,10 @@
         <v>36</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>36</v>
@@ -11542,14 +11543,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11568,19 +11569,19 @@
         <v>36</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>36</v>
@@ -11605,11 +11606,9 @@
         <v>36</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
         <v>481</v>
       </c>
@@ -11629,7 +11628,7 @@
         <v>36</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>34</v>
@@ -11638,10 +11637,10 @@
         <v>35</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>36</v>
@@ -11760,10 +11759,10 @@
         <v>35</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>36</v>
@@ -11800,7 +11799,7 @@
         <v>34</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>36</v>
@@ -11812,7 +11811,7 @@
         <v>36</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>495</v>
@@ -11847,7 +11846,7 @@
         <v>36</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y79" t="s" s="2">
         <v>498</v>
@@ -11877,13 +11876,13 @@
         <v>34</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>36</v>
@@ -11920,7 +11919,7 @@
         <v>34</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>36</v>
@@ -11932,7 +11931,7 @@
         <v>36</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>505</v>
@@ -11969,7 +11968,7 @@
         <v>36</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y80" t="s" s="2">
         <v>509</v>
@@ -11999,13 +11998,13 @@
         <v>34</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>36</v>
@@ -12042,7 +12041,7 @@
         <v>34</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>36</v>
@@ -12119,13 +12118,13 @@
         <v>34</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>36</v>
@@ -12162,7 +12161,7 @@
         <v>34</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>36</v>
@@ -12239,13 +12238,13 @@
         <v>34</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>36</v>
@@ -12364,7 +12363,7 @@
         <v>35</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>537</v>
@@ -12404,7 +12403,7 @@
         <v>34</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>36</v>
@@ -12416,13 +12415,13 @@
         <v>36</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12473,13 +12472,13 @@
         <v>36</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>36</v>
@@ -12497,7 +12496,7 @@
         <v>36</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>36</v>
@@ -12515,7 +12514,7 @@
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12534,16 +12533,16 @@
         <v>36</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12581,19 +12580,19 @@
         <v>36</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>34</v>
@@ -12602,10 +12601,10 @@
         <v>35</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>36</v>
@@ -12617,7 +12616,7 @@
         <v>36</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>36</v>
@@ -12648,13 +12647,13 @@
         <v>36</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>544</v>
@@ -12663,10 +12662,10 @@
         <v>545</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>36</v>
@@ -12724,10 +12723,10 @@
         <v>35</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>36</v>
@@ -12739,7 +12738,7 @@
         <v>36</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>36</v>
@@ -12764,7 +12763,7 @@
         <v>34</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>36</v>
@@ -12841,7 +12840,7 @@
         <v>34</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>552</v>
@@ -12884,7 +12883,7 @@
         <v>34</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>36</v>
@@ -12961,7 +12960,7 @@
         <v>34</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>552</v>
@@ -13004,7 +13003,7 @@
         <v>34</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>36</v>
@@ -13016,7 +13015,7 @@
         <v>36</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>561</v>
@@ -13053,7 +13052,7 @@
         <v>36</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y89" t="s" s="2">
         <v>565</v>
@@ -13083,13 +13082,13 @@
         <v>34</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>36</v>
@@ -13138,7 +13137,7 @@
         <v>36</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>570</v>
@@ -13175,7 +13174,7 @@
         <v>36</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y90" t="s" s="2">
         <v>574</v>
@@ -13208,10 +13207,10 @@
         <v>35</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>36</v>
@@ -13248,7 +13247,7 @@
         <v>34</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>36</v>
@@ -13327,10 +13326,10 @@
         <v>34</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>582</v>
@@ -13370,7 +13369,7 @@
         <v>34</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>36</v>
@@ -13382,7 +13381,7 @@
         <v>36</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>586</v>
@@ -13391,7 +13390,7 @@
         <v>587</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13447,13 +13446,13 @@
         <v>34</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>36</v>
@@ -13499,7 +13498,7 @@
         <v>36</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K93" t="s" s="2">
         <v>590</v>
@@ -13570,10 +13569,10 @@
         <v>35</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>36</v>
@@ -13619,7 +13618,7 @@
         <v>36</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>597</v>
@@ -13690,10 +13689,10 @@
         <v>35</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>36</v>
@@ -13733,13 +13732,13 @@
         <v>35</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>532</v>
@@ -13812,7 +13811,7 @@
         <v>35</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>606</v>
@@ -13852,7 +13851,7 @@
         <v>34</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>36</v>
@@ -13864,13 +13863,13 @@
         <v>36</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13921,13 +13920,13 @@
         <v>36</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>36</v>
@@ -13945,7 +13944,7 @@
         <v>36</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>36</v>
@@ -13963,7 +13962,7 @@
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13982,16 +13981,16 @@
         <v>36</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14029,19 +14028,19 @@
         <v>36</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>34</v>
@@ -14050,10 +14049,10 @@
         <v>35</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>36</v>
@@ -14065,7 +14064,7 @@
         <v>36</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>36</v>
@@ -14096,13 +14095,13 @@
         <v>36</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L98" t="s" s="2">
         <v>544</v>
@@ -14111,10 +14110,10 @@
         <v>545</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>36</v>
@@ -14172,10 +14171,10 @@
         <v>35</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>36</v>
@@ -14187,7 +14186,7 @@
         <v>36</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>36</v>
@@ -14209,22 +14208,22 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L99" t="s" s="2">
         <v>613</v>
@@ -14261,13 +14260,13 @@
         <v>36</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>36</v>
@@ -14288,16 +14287,16 @@
         <v>612</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>36</v>
@@ -14306,13 +14305,13 @@
         <v>617</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>36</v>
@@ -14334,16 +14333,16 @@
         <v>34</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>619</v>
@@ -14358,7 +14357,7 @@
         <v>622</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>36</v>
@@ -14383,7 +14382,7 @@
         <v>36</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y100" t="s" s="2">
         <v>623</v>
@@ -14413,13 +14412,13 @@
         <v>34</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>625</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>36</v>
@@ -14428,16 +14427,16 @@
         <v>626</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="101" hidden="true">
@@ -14456,10 +14455,10 @@
         <v>34</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>36</v>
@@ -14468,7 +14467,7 @@
         <v>36</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L101" t="s" s="2">
         <v>628</v>
@@ -14480,7 +14479,7 @@
         <v>630</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>36</v>
@@ -14505,13 +14504,13 @@
         <v>36</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>36</v>
@@ -14535,13 +14534,13 @@
         <v>34</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>631</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>36</v>
@@ -14550,10 +14549,10 @@
         <v>36</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>36</v>
@@ -14571,7 +14570,7 @@
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14590,19 +14589,19 @@
         <v>36</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>36</v>
@@ -14627,13 +14626,13 @@
         <v>36</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>480</v>
+        <v>633</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>633</v>
+        <v>481</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>36</v>
@@ -14660,10 +14659,10 @@
         <v>35</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>36</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:09:26+00:00</t>
+    <t>2023-09-19T16:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:18:04+00:00</t>
+    <t>2023-09-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T15:08:45+00:00</t>
+    <t>2023-09-27T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:45:14+00:00</t>
+    <t>2023-11-23T10:14:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-23T10:14:09+00:00</t>
+    <t>2023-11-28T12:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -440,11 +440,10 @@
 </t>
   </si>
   <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.</t>
-  </si>
-  <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.
-L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4033" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4032" uniqueCount="680">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:14:54+00:00</t>
+    <t>2023-11-28T12:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1733,9 +1733,6 @@
   </si>
   <si>
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J158-MethodStepsByDay-ENS/FHIR/JDV-J158-MethodStepsByDay-ENS</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J146-MethodBodyHeight-ENS/FHIR/JDV-J146-MethodBodyHeight-ENS</t>
@@ -12190,7 +12187,7 @@
         <v>91</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>80</v>
@@ -12236,13 +12233,11 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y81" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y81" s="2"/>
+      <c r="Z81" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -12281,10 +12276,10 @@
         <v>80</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -12295,10 +12290,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12321,16 +12316,16 @@
         <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12380,7 +12375,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12398,27 +12393,27 @@
         <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM82" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="AM82" t="s" s="2">
+      <c r="AN82" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AN82" t="s" s="2">
+      <c r="AO82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP82" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>565</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12441,16 +12436,16 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12500,7 +12495,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12518,27 +12513,27 @@
         <v>80</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>574</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12561,19 +12556,19 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -12622,7 +12617,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12634,19 +12629,19 @@
         <v>103</v>
       </c>
       <c r="AJ84" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="AK84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12657,10 +12652,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12775,10 +12770,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12895,14 +12890,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12924,10 +12919,10 @@
         <v>114</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>117</v>
@@ -12982,7 +12977,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -13017,10 +13012,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13043,16 +13038,16 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13102,7 +13097,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13111,22 +13106,22 @@
         <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AJ88" t="s" s="2">
+      <c r="AK88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM88" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AK88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM88" t="s" s="2">
+      <c r="AN88" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -13137,10 +13132,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13163,16 +13158,16 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="M89" t="s" s="2">
-        <v>602</v>
-      </c>
       <c r="N89" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13222,7 +13217,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13231,22 +13226,22 @@
         <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AJ89" t="s" s="2">
+      <c r="AK89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AK89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>598</v>
-      </c>
       <c r="AN89" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
@@ -13257,10 +13252,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13286,16 +13281,16 @@
         <v>254</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -13323,11 +13318,11 @@
         <v>175</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="Z90" t="s" s="2">
-        <v>610</v>
-      </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
       </c>
@@ -13344,7 +13339,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13362,10 +13357,10 @@
         <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>528</v>
@@ -13379,10 +13374,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13408,16 +13403,16 @@
         <v>254</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -13445,11 +13440,11 @@
         <v>161</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="Z91" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="Z91" t="s" s="2">
-        <v>619</v>
-      </c>
       <c r="AA91" t="s" s="2">
         <v>80</v>
       </c>
@@ -13466,7 +13461,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13484,10 +13479,10 @@
         <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM91" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>528</v>
@@ -13501,10 +13496,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13527,19 +13522,19 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13588,7 +13583,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13600,19 +13595,19 @@
         <v>103</v>
       </c>
       <c r="AJ92" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="AK92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM92" t="s" s="2">
+      <c r="AN92" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -13623,10 +13618,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13652,10 +13647,10 @@
         <v>107</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>306</v>
@@ -13708,7 +13703,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13729,10 +13724,10 @@
         <v>80</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13743,10 +13738,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13769,16 +13764,16 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13828,7 +13823,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13849,10 +13844,10 @@
         <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13863,10 +13858,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13889,16 +13884,16 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13948,7 +13943,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13969,10 +13964,10 @@
         <v>80</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
@@ -13983,10 +13978,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14009,19 +14004,19 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="M96" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -14070,7 +14065,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -14082,19 +14077,19 @@
         <v>103</v>
       </c>
       <c r="AJ96" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM96" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="AK96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM96" t="s" s="2">
+      <c r="AN96" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -14105,10 +14100,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14223,10 +14218,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14343,14 +14338,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14372,10 +14367,10 @@
         <v>114</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>117</v>
@@ -14430,7 +14425,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14465,10 +14460,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14494,16 +14489,16 @@
         <v>254</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14552,7 +14547,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -14570,7 +14565,7 @@
         <v>80</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>349</v>
@@ -14587,10 +14582,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14613,16 +14608,16 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>436</v>
@@ -14653,11 +14648,11 @@
         <v>245</v>
       </c>
       <c r="Y101" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="Z101" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="Z101" t="s" s="2">
-        <v>668</v>
-      </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
       </c>
@@ -14674,7 +14669,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14683,7 +14678,7 @@
         <v>91</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>104</v>
@@ -14692,7 +14687,7 @@
         <v>80</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>441</v>
@@ -14709,10 +14704,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14738,13 +14733,13 @@
         <v>254</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>503</v>
@@ -14796,7 +14791,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14805,7 +14800,7 @@
         <v>91</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>104</v>
@@ -14831,10 +14826,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14897,7 +14892,7 @@
         <v>151</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="Z103" t="s" s="2">
         <v>525</v>
@@ -14918,7 +14913,7 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14953,10 +14948,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14982,16 +14977,16 @@
         <v>81</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="M104" t="s" s="2">
-        <v>680</v>
-      </c>
       <c r="N104" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O104" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -15040,7 +15035,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -15061,10 +15056,10 @@
         <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4032" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4033" uniqueCount="681">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:15:35+00:00</t>
+    <t>2023-11-28T12:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1733,6 +1733,9 @@
   </si>
   <si>
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J158-MethodStepsByDay-ENS/FHIR/JDV-J158-MethodStepsByDay-ENS</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J146-MethodBodyHeight-ENS/FHIR/JDV-J146-MethodBodyHeight-ENS</t>
@@ -12187,7 +12190,7 @@
         <v>91</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>80</v>
@@ -12233,11 +12236,13 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y81" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="Z81" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -12276,10 +12281,10 @@
         <v>80</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -12290,10 +12295,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12316,16 +12321,16 @@
         <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12375,7 +12380,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12393,27 +12398,27 @@
         <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12436,16 +12441,16 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12495,7 +12500,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12513,27 +12518,27 @@
         <v>80</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12556,19 +12561,19 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -12617,7 +12622,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12629,7 +12634,7 @@
         <v>103</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>80</v>
@@ -12638,10 +12643,10 @@
         <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12652,10 +12657,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12770,10 +12775,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12890,14 +12895,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12919,10 +12924,10 @@
         <v>114</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>117</v>
@@ -12977,7 +12982,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -13012,10 +13017,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13038,16 +13043,16 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13097,7 +13102,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13106,10 +13111,10 @@
         <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>80</v>
@@ -13118,10 +13123,10 @@
         <v>80</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -13132,10 +13137,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13158,16 +13163,16 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13217,7 +13222,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13226,10 +13231,10 @@
         <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>80</v>
@@ -13238,10 +13243,10 @@
         <v>80</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
@@ -13252,10 +13257,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13281,16 +13286,16 @@
         <v>254</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -13318,10 +13323,10 @@
         <v>175</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -13339,7 +13344,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13357,10 +13362,10 @@
         <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>528</v>
@@ -13374,10 +13379,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13403,16 +13408,16 @@
         <v>254</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -13440,10 +13445,10 @@
         <v>161</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>80</v>
@@ -13461,7 +13466,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13479,10 +13484,10 @@
         <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>528</v>
@@ -13496,10 +13501,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13522,19 +13527,19 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13583,7 +13588,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13595,7 +13600,7 @@
         <v>103</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>80</v>
@@ -13604,10 +13609,10 @@
         <v>80</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -13618,10 +13623,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13647,10 +13652,10 @@
         <v>107</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>306</v>
@@ -13703,7 +13708,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13724,10 +13729,10 @@
         <v>80</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13738,10 +13743,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13764,16 +13769,16 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13823,7 +13828,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13844,10 +13849,10 @@
         <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13858,10 +13863,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13884,16 +13889,16 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13943,7 +13948,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13964,10 +13969,10 @@
         <v>80</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
@@ -13978,10 +13983,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14004,19 +14009,19 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -14065,7 +14070,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -14077,7 +14082,7 @@
         <v>103</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>80</v>
@@ -14086,10 +14091,10 @@
         <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -14100,10 +14105,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14218,10 +14223,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14338,14 +14343,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14367,10 +14372,10 @@
         <v>114</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>117</v>
@@ -14425,7 +14430,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14460,10 +14465,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14489,16 +14494,16 @@
         <v>254</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14547,7 +14552,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -14565,7 +14570,7 @@
         <v>80</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>349</v>
@@ -14582,10 +14587,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14608,16 +14613,16 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>436</v>
@@ -14648,10 +14653,10 @@
         <v>245</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -14669,7 +14674,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14678,7 +14683,7 @@
         <v>91</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>104</v>
@@ -14687,7 +14692,7 @@
         <v>80</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>441</v>
@@ -14704,10 +14709,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14733,13 +14738,13 @@
         <v>254</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>503</v>
@@ -14791,7 +14796,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14800,7 +14805,7 @@
         <v>91</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>104</v>
@@ -14826,10 +14831,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14892,7 +14897,7 @@
         <v>151</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="Z103" t="s" s="2">
         <v>525</v>
@@ -14913,7 +14918,7 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14948,10 +14953,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14977,16 +14982,16 @@
         <v>81</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -15035,7 +15040,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -15056,10 +15061,10 @@
         <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4033" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4032" uniqueCount="680">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:22:20+00:00</t>
+    <t>2023-11-28T12:44:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1733,9 +1733,6 @@
   </si>
   <si>
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J158-MethodStepsByDay-ENS/FHIR/JDV-J158-MethodStepsByDay-ENS</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J146-MethodBodyHeight-ENS/FHIR/JDV-J146-MethodBodyHeight-ENS</t>
@@ -12190,7 +12187,7 @@
         <v>91</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>80</v>
@@ -12236,13 +12233,11 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y81" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y81" s="2"/>
+      <c r="Z81" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -12281,10 +12276,10 @@
         <v>80</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -12295,10 +12290,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12321,16 +12316,16 @@
         <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12380,7 +12375,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12398,27 +12393,27 @@
         <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM82" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="AM82" t="s" s="2">
+      <c r="AN82" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AN82" t="s" s="2">
+      <c r="AO82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP82" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>565</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12441,16 +12436,16 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12500,7 +12495,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12518,27 +12513,27 @@
         <v>80</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AN83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>574</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12561,19 +12556,19 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -12622,7 +12617,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12634,19 +12629,19 @@
         <v>103</v>
       </c>
       <c r="AJ84" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="AK84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12657,10 +12652,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12775,10 +12770,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12895,14 +12890,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12924,10 +12919,10 @@
         <v>114</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>117</v>
@@ -12982,7 +12977,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -13017,10 +13012,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13043,16 +13038,16 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13102,7 +13097,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13111,22 +13106,22 @@
         <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AJ88" t="s" s="2">
+      <c r="AK88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM88" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AK88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM88" t="s" s="2">
+      <c r="AN88" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -13137,10 +13132,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13163,16 +13158,16 @@
         <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="M89" t="s" s="2">
-        <v>602</v>
-      </c>
       <c r="N89" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13222,7 +13217,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13231,22 +13226,22 @@
         <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AJ89" t="s" s="2">
+      <c r="AK89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AK89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>598</v>
-      </c>
       <c r="AN89" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
@@ -13257,10 +13252,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13286,16 +13281,16 @@
         <v>254</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -13323,11 +13318,11 @@
         <v>175</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="Z90" t="s" s="2">
-        <v>610</v>
-      </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
       </c>
@@ -13344,7 +13339,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13362,10 +13357,10 @@
         <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>528</v>
@@ -13379,10 +13374,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13408,16 +13403,16 @@
         <v>254</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -13445,11 +13440,11 @@
         <v>161</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="Z91" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="Z91" t="s" s="2">
-        <v>619</v>
-      </c>
       <c r="AA91" t="s" s="2">
         <v>80</v>
       </c>
@@ -13466,7 +13461,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13484,10 +13479,10 @@
         <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM91" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>528</v>
@@ -13501,10 +13496,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13527,19 +13522,19 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13588,7 +13583,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13600,19 +13595,19 @@
         <v>103</v>
       </c>
       <c r="AJ92" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="AK92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM92" t="s" s="2">
+      <c r="AN92" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -13623,10 +13618,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13652,10 +13647,10 @@
         <v>107</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>306</v>
@@ -13708,7 +13703,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13729,10 +13724,10 @@
         <v>80</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13743,10 +13738,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13769,16 +13764,16 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13828,7 +13823,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13849,10 +13844,10 @@
         <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13863,10 +13858,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13889,16 +13884,16 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13948,7 +13943,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13969,10 +13964,10 @@
         <v>80</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
@@ -13983,10 +13978,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14009,19 +14004,19 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="M96" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -14070,7 +14065,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -14082,19 +14077,19 @@
         <v>103</v>
       </c>
       <c r="AJ96" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM96" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="AK96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM96" t="s" s="2">
+      <c r="AN96" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -14105,10 +14100,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14223,10 +14218,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14343,14 +14338,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14372,10 +14367,10 @@
         <v>114</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>117</v>
@@ -14430,7 +14425,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14465,10 +14460,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14494,16 +14489,16 @@
         <v>254</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14552,7 +14547,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>91</v>
@@ -14570,7 +14565,7 @@
         <v>80</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>349</v>
@@ -14587,10 +14582,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14613,16 +14608,16 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>436</v>
@@ -14653,11 +14648,11 @@
         <v>245</v>
       </c>
       <c r="Y101" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="Z101" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="Z101" t="s" s="2">
-        <v>668</v>
-      </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
       </c>
@@ -14674,7 +14669,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14683,7 +14678,7 @@
         <v>91</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>104</v>
@@ -14692,7 +14687,7 @@
         <v>80</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>441</v>
@@ -14709,10 +14704,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14738,13 +14733,13 @@
         <v>254</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>503</v>
@@ -14796,7 +14791,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14805,7 +14800,7 @@
         <v>91</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>104</v>
@@ -14831,10 +14826,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14897,7 +14892,7 @@
         <v>151</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="Z103" t="s" s="2">
         <v>525</v>
@@ -14918,7 +14913,7 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14953,10 +14948,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14982,16 +14977,16 @@
         <v>81</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="M104" t="s" s="2">
-        <v>680</v>
-      </c>
       <c r="N104" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O104" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -15040,7 +15035,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -15061,10 +15056,10 @@
         <v>80</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:44:29+00:00</t>
+    <t>2023-11-28T13:07:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:07:26+00:00</t>
+    <t>2023-11-28T13:18:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1779,11 +1779,11 @@
 </t>
   </si>
   <si>
-    <t>Dispositif utilisé pour l'observation</t>
-  </si>
-  <si>
     <t>Dispositif utilisé pour l'observation
-Si la mesure a été faite par un objet connecté (Profil PhdDevice) =&gt;cette référence est obligatoire</t>
+Si la mesure a été faite par un objet connecté (Profil PhdDevice), cette référence est obligatoire</t>
+  </si>
+  <si>
+    <t>The device used to generate the observation data.</t>
   </si>
   <si>
     <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
@@ -12427,7 +12427,7 @@
         <v>91</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>80</v>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:18:47+00:00</t>
+    <t>2023-11-28T13:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:27:45+00:00</t>
+    <t>2023-11-28T13:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:42:11+00:00</t>
+    <t>2023-12-08T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T10:33:05+00:00</t>
+    <t>2023-12-29T10:04:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T10:04:05+00:00</t>
+    <t>2024-02-01T10:35:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T10:35:02+00:00</t>
+    <t>2024-02-01T13:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:55:30+00:00</t>
+    <t>2024-02-01T13:56:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:56:11+00:00</t>
+    <t>2024-02-01T14:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T14:29:51+00:00</t>
+    <t>2024-02-01T16:04:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T16:04:25+00:00</t>
+    <t>2024-02-05T14:48:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T14:48:49+00:00</t>
+    <t>2024-02-12T14:46:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:46:58+00:00</t>
+    <t>2024-02-12T14:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:53:29+00:00</t>
+    <t>2024-04-08T08:01:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
